--- a/data/semanas/323_pe.xlsx
+++ b/data/semanas/323_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL11"/>
+  <dimension ref="A1:AL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1179,7 +1179,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17381101</v>
+        <v>17432944</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4 -PE</t>
+          <t>419 - CENTRO 5 PE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua 15 DENOVEMBRO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2720 - C</t>
+          <t>67 - C</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>09/09/2026 08:21</t>
+          <t>09/09/2026 08:05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09/09/2026 08:29</t>
+          <t>09/09/2026 08:16</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46274.34791666667</v>
+        <v>46274.33680555555</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>46274.35347222222</v>
+        <v>46274.34444444445</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>46274</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>80040</v>
+        <v>79080</v>
       </c>
       <c r="AB6" t="b">
         <v>0</v>
@@ -1292,7 +1292,7 @@
         <v>8</v>
       </c>
       <c r="AF6" t="n">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17381102</v>
+        <v>17381101</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1326,22 +1326,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>422 VILA TORRES PE</t>
+          <t>418 - CENTRO 4 -PE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua TIRADENTES</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1003 - C</t>
+          <t>2720 - C</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09/09/2026 08:37</t>
+          <t>09/09/2026 08:21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>09/09/2026 08:46</t>
+          <t>09/09/2026 08:29</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46274.35902777778</v>
+        <v>46274.34791666667</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>46274.36527777778</v>
+        <v>46274.35347222222</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>46274</v>
@@ -1430,7 +1430,7 @@
         <v>8</v>
       </c>
       <c r="AF7" t="n">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17381103</v>
+        <v>17381102</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1464,22 +1464,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS - PE</t>
+          <t>422 VILA TORRES PE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua 18 DE JULHO</t>
+          <t>Rua TIRADENTES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>240 - C</t>
+          <t>1003 - C</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>09/09/2026 08:53</t>
+          <t>09/09/2026 08:37</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>09/09/2026 09:08</t>
+          <t>09/09/2026 08:46</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>46274.37013888889</v>
+        <v>46274.35902777778</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>46274.38055555556</v>
+        <v>46274.36527777778</v>
       </c>
       <c r="P8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>46274</v>
@@ -1568,7 +1568,7 @@
         <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17381104</v>
+        <v>17381103</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1607,17 +1607,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua PARAGUAI</t>
+          <t>Rua 18 DE JULHO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>426 - 2 - C</t>
+          <t>240 - C</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>09/09/2026 09:10</t>
+          <t>09/09/2026 08:53</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>09/09/2026 09:27</t>
+          <t>09/09/2026 09:08</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>46274.38194444445</v>
+        <v>46274.37013888889</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>46274.39375</v>
+        <v>46274.38055555556</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>46274</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1020</v>
+        <v>960</v>
       </c>
       <c r="AB9" t="b">
         <v>0</v>
@@ -1703,10 +1703,10 @@
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF9" t="n">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17381105</v>
+        <v>17381104</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Avenida INTERNACIONAL</t>
+          <t>Rua PARAGUAI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>703 - C</t>
+          <t>426 - 2 - C</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>09/09/2026 09:29</t>
+          <t>09/09/2026 09:10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>09/09/2026 09:48</t>
+          <t>09/09/2026 09:27</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>46274.39513888889</v>
+        <v>46274.38194444445</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>46274.40833333333</v>
+        <v>46274.39375</v>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>46274</v>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1140</v>
+        <v>1020</v>
       </c>
       <c r="AB10" t="b">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>9</v>
       </c>
       <c r="AF10" t="n">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17381106</v>
+        <v>17381105</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>510 - 1 - C</t>
+          <t>703 - C</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>09/09/2026 09:52</t>
+          <t>09/09/2026 09:29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>09/09/2026 10:11</t>
+          <t>09/09/2026 09:48</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>46274.41111111111</v>
+        <v>46274.39513888889</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>46274.42430555556</v>
+        <v>46274.40833333333</v>
       </c>
       <c r="P11" t="n">
         <v>19</v>
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1380</v>
+        <v>1140</v>
       </c>
       <c r="AB11" t="b">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2002,6 +2002,144 @@
         <v>1</v>
       </c>
       <c r="AL11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>17381106</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>414 - PARQUE DOS ERVAIS - PE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>510 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>09/09/2026 09:52</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>09/09/2026 10:11</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>46274.41111111111</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>46274.42430555556</v>
+      </c>
+      <c r="P12" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="R12" t="n">
+        <v>323</v>
+      </c>
+      <c r="S12" t="n">
+        <v>36</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1380</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>592</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="b">
         <v>0</v>
       </c>
     </row>
